--- a/REQUIREMENTS-TEMPLATE.xlsx
+++ b/REQUIREMENTS-TEMPLATE.xlsx
@@ -442,7 +442,7 @@
     <col min="39" max="39" width="20.83203125" customWidth="1"/>
     <col min="40" max="40" width="14.83203125" customWidth="1"/>
     <col min="41" max="41" width="14.83203125" customWidth="1"/>
-    <col min="42" max="42" width="10.83203125" customWidth="1"/>
+    <col min="42" max="42" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -570,7 +570,7 @@
         <v>verified_at</v>
       </c>
       <c r="AP1" t="str">
-        <v>source</v>
+        <v>generated_by</v>
       </c>
     </row>
     <row r="2">
@@ -698,7 +698,7 @@
         <v/>
       </c>
       <c r="AP2" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="3">
@@ -826,7 +826,7 @@
         <v/>
       </c>
       <c r="AP3" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="4">
@@ -954,7 +954,7 @@
         <v/>
       </c>
       <c r="AP4" t="str">
-        <v>claude</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="5">
@@ -1082,7 +1082,7 @@
         <v/>
       </c>
       <c r="AP5" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="6">
@@ -1210,7 +1210,7 @@
         <v/>
       </c>
       <c r="AP6" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="7">
@@ -1338,7 +1338,7 @@
         <v/>
       </c>
       <c r="AP7" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="8">
@@ -1466,7 +1466,7 @@
         <v/>
       </c>
       <c r="AP8" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="9">
@@ -1594,7 +1594,7 @@
         <v/>
       </c>
       <c r="AP9" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="10">
@@ -1722,7 +1722,7 @@
         <v/>
       </c>
       <c r="AP10" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="11">
@@ -1850,7 +1850,7 @@
         <v/>
       </c>
       <c r="AP11" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="12">
@@ -1978,7 +1978,7 @@
         <v/>
       </c>
       <c r="AP12" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="13">
@@ -2106,7 +2106,7 @@
         <v/>
       </c>
       <c r="AP13" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="14">
@@ -2234,7 +2234,7 @@
         <v/>
       </c>
       <c r="AP14" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="15">
@@ -2362,7 +2362,7 @@
         <v/>
       </c>
       <c r="AP15" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="16">
@@ -2490,7 +2490,7 @@
         <v/>
       </c>
       <c r="AP16" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="17">
@@ -2618,7 +2618,7 @@
         <v/>
       </c>
       <c r="AP17" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="18">
@@ -2746,7 +2746,7 @@
         <v/>
       </c>
       <c r="AP18" t="str">
-        <v>claude</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="19">
@@ -2874,7 +2874,7 @@
         <v/>
       </c>
       <c r="AP19" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="20">
@@ -3002,7 +3002,7 @@
         <v/>
       </c>
       <c r="AP20" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="21">
@@ -3130,7 +3130,7 @@
         <v/>
       </c>
       <c r="AP21" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="22">
@@ -3258,7 +3258,7 @@
         <v/>
       </c>
       <c r="AP22" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="23">
@@ -3386,7 +3386,7 @@
         <v/>
       </c>
       <c r="AP23" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="24">
@@ -3514,7 +3514,7 @@
         <v/>
       </c>
       <c r="AP24" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="25">
@@ -3642,7 +3642,7 @@
         <v/>
       </c>
       <c r="AP25" t="str">
-        <v>claude</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="26">
@@ -3770,7 +3770,7 @@
         <v/>
       </c>
       <c r="AP26" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="27">
@@ -3898,7 +3898,7 @@
         <v/>
       </c>
       <c r="AP27" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="28">
@@ -4026,7 +4026,7 @@
         <v/>
       </c>
       <c r="AP28" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="29">
@@ -4154,7 +4154,7 @@
         <v/>
       </c>
       <c r="AP29" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="30">
@@ -4282,7 +4282,7 @@
         <v/>
       </c>
       <c r="AP30" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="31">
@@ -4410,7 +4410,7 @@
         <v/>
       </c>
       <c r="AP31" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="32">
@@ -4538,7 +4538,7 @@
         <v/>
       </c>
       <c r="AP32" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="33">
@@ -4666,7 +4666,7 @@
         <v/>
       </c>
       <c r="AP33" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="34">
@@ -4794,7 +4794,7 @@
         <v/>
       </c>
       <c r="AP34" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="35">
@@ -4922,7 +4922,7 @@
         <v/>
       </c>
       <c r="AP35" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="36">
@@ -5050,7 +5050,7 @@
         <v/>
       </c>
       <c r="AP36" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="37">
@@ -5178,7 +5178,7 @@
         <v/>
       </c>
       <c r="AP37" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="38">
@@ -5306,7 +5306,7 @@
         <v/>
       </c>
       <c r="AP38" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="39">
@@ -5434,7 +5434,7 @@
         <v/>
       </c>
       <c r="AP39" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="40">
@@ -5562,7 +5562,7 @@
         <v/>
       </c>
       <c r="AP40" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="41">
@@ -5690,7 +5690,7 @@
         <v/>
       </c>
       <c r="AP41" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="42">
@@ -5818,7 +5818,7 @@
         <v/>
       </c>
       <c r="AP42" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="43">
@@ -5946,7 +5946,7 @@
         <v/>
       </c>
       <c r="AP43" t="str">
-        <v>claude</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="44">
@@ -6074,7 +6074,7 @@
         <v/>
       </c>
       <c r="AP44" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="45">
@@ -6202,7 +6202,7 @@
         <v/>
       </c>
       <c r="AP45" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="46">
@@ -6330,7 +6330,7 @@
         <v/>
       </c>
       <c r="AP46" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="47">
@@ -6458,7 +6458,7 @@
         <v/>
       </c>
       <c r="AP47" t="str">
-        <v>claude</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="48">
@@ -6586,7 +6586,7 @@
         <v/>
       </c>
       <c r="AP48" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="49">
@@ -6714,7 +6714,7 @@
         <v/>
       </c>
       <c r="AP49" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="50">
@@ -6842,7 +6842,7 @@
         <v/>
       </c>
       <c r="AP50" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="51">
@@ -6970,7 +6970,7 @@
         <v/>
       </c>
       <c r="AP51" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="52">
@@ -7098,7 +7098,7 @@
         <v/>
       </c>
       <c r="AP52" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="53">
@@ -7226,7 +7226,7 @@
         <v/>
       </c>
       <c r="AP53" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="54">
@@ -7354,7 +7354,7 @@
         <v/>
       </c>
       <c r="AP54" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="55">
@@ -7482,7 +7482,7 @@
         <v/>
       </c>
       <c r="AP55" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="56">
@@ -7610,7 +7610,7 @@
         <v/>
       </c>
       <c r="AP56" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="57">
@@ -7738,7 +7738,7 @@
         <v/>
       </c>
       <c r="AP57" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="58">
@@ -7866,7 +7866,7 @@
         <v/>
       </c>
       <c r="AP58" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="59">
@@ -7994,7 +7994,7 @@
         <v/>
       </c>
       <c r="AP59" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="60">
@@ -8122,7 +8122,7 @@
         <v/>
       </c>
       <c r="AP60" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="61">
@@ -8250,7 +8250,7 @@
         <v/>
       </c>
       <c r="AP61" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="62">
@@ -8378,7 +8378,7 @@
         <v/>
       </c>
       <c r="AP62" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="63">
@@ -8506,7 +8506,7 @@
         <v/>
       </c>
       <c r="AP63" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="64">
@@ -8634,7 +8634,7 @@
         <v/>
       </c>
       <c r="AP64" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="65">
@@ -8762,7 +8762,7 @@
         <v/>
       </c>
       <c r="AP65" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="66">
@@ -8890,7 +8890,7 @@
         <v/>
       </c>
       <c r="AP66" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="67">
@@ -9018,7 +9018,7 @@
         <v/>
       </c>
       <c r="AP67" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="68">
@@ -9146,7 +9146,7 @@
         <v/>
       </c>
       <c r="AP68" t="str">
-        <v>claude</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="69">
@@ -9274,7 +9274,7 @@
         <v/>
       </c>
       <c r="AP69" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="70">
@@ -9402,7 +9402,7 @@
         <v/>
       </c>
       <c r="AP70" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="71">
@@ -9530,7 +9530,7 @@
         <v/>
       </c>
       <c r="AP71" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="72">
@@ -9658,7 +9658,7 @@
         <v/>
       </c>
       <c r="AP72" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="73">
@@ -9786,7 +9786,7 @@
         <v/>
       </c>
       <c r="AP73" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="74">
@@ -9914,7 +9914,7 @@
         <v/>
       </c>
       <c r="AP74" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="75">
@@ -10042,7 +10042,7 @@
         <v/>
       </c>
       <c r="AP75" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="76">
@@ -10170,7 +10170,7 @@
         <v/>
       </c>
       <c r="AP76" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="77">
@@ -10298,7 +10298,7 @@
         <v/>
       </c>
       <c r="AP77" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="78">
@@ -10426,7 +10426,7 @@
         <v/>
       </c>
       <c r="AP78" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="79">
@@ -10554,7 +10554,7 @@
         <v/>
       </c>
       <c r="AP79" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="80">
@@ -10682,7 +10682,7 @@
         <v/>
       </c>
       <c r="AP80" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="81">
@@ -10810,7 +10810,7 @@
         <v/>
       </c>
       <c r="AP81" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="82">
@@ -10938,7 +10938,7 @@
         <v/>
       </c>
       <c r="AP82" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="83">
@@ -11066,7 +11066,7 @@
         <v/>
       </c>
       <c r="AP83" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="84">
@@ -11194,7 +11194,7 @@
         <v/>
       </c>
       <c r="AP84" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="85">
@@ -11322,7 +11322,7 @@
         <v/>
       </c>
       <c r="AP85" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="86">
@@ -11450,7 +11450,7 @@
         <v/>
       </c>
       <c r="AP86" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="87">
@@ -11578,7 +11578,7 @@
         <v/>
       </c>
       <c r="AP87" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="88">
@@ -11706,7 +11706,7 @@
         <v/>
       </c>
       <c r="AP88" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="89">
@@ -11834,7 +11834,7 @@
         <v/>
       </c>
       <c r="AP89" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="90">
@@ -11962,7 +11962,7 @@
         <v/>
       </c>
       <c r="AP90" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="91">
@@ -12090,7 +12090,7 @@
         <v/>
       </c>
       <c r="AP91" t="str">
-        <v>claude</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="92">
@@ -12218,7 +12218,7 @@
         <v/>
       </c>
       <c r="AP92" t="str">
-        <v>claude</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="93">
@@ -12346,7 +12346,7 @@
         <v/>
       </c>
       <c r="AP93" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="94">
@@ -12474,7 +12474,7 @@
         <v/>
       </c>
       <c r="AP94" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="95">
@@ -12602,7 +12602,7 @@
         <v/>
       </c>
       <c r="AP95" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="96">
@@ -12730,7 +12730,7 @@
         <v/>
       </c>
       <c r="AP96" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="97">
@@ -12858,7 +12858,7 @@
         <v/>
       </c>
       <c r="AP97" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="98">
@@ -12986,7 +12986,7 @@
         <v/>
       </c>
       <c r="AP98" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="99">
@@ -13114,7 +13114,7 @@
         <v/>
       </c>
       <c r="AP99" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="100">
@@ -13242,7 +13242,7 @@
         <v/>
       </c>
       <c r="AP100" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="101">
@@ -13370,7 +13370,7 @@
         <v/>
       </c>
       <c r="AP101" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="102">
@@ -13498,7 +13498,7 @@
         <v/>
       </c>
       <c r="AP102" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="103">
@@ -13626,7 +13626,7 @@
         <v/>
       </c>
       <c r="AP103" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="104">
@@ -13754,7 +13754,7 @@
         <v/>
       </c>
       <c r="AP104" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="105">
@@ -13882,7 +13882,7 @@
         <v/>
       </c>
       <c r="AP105" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="106">
@@ -14010,7 +14010,7 @@
         <v/>
       </c>
       <c r="AP106" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="107">
@@ -14138,7 +14138,7 @@
         <v/>
       </c>
       <c r="AP107" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="108">
@@ -14266,7 +14266,7 @@
         <v/>
       </c>
       <c r="AP108" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="109">
@@ -14394,7 +14394,7 @@
         <v/>
       </c>
       <c r="AP109" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="110">
@@ -14522,7 +14522,7 @@
         <v/>
       </c>
       <c r="AP110" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="111">
@@ -14650,7 +14650,7 @@
         <v/>
       </c>
       <c r="AP111" t="str">
-        <v>claude</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="112">
@@ -14778,7 +14778,7 @@
         <v/>
       </c>
       <c r="AP112" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="113">
@@ -14906,7 +14906,7 @@
         <v/>
       </c>
       <c r="AP113" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="114">
@@ -15034,7 +15034,7 @@
         <v/>
       </c>
       <c r="AP114" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="115">
@@ -15162,7 +15162,7 @@
         <v/>
       </c>
       <c r="AP115" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="116">
@@ -15290,7 +15290,7 @@
         <v/>
       </c>
       <c r="AP116" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="117">
@@ -15418,7 +15418,7 @@
         <v/>
       </c>
       <c r="AP117" t="str">
-        <v>gemini</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="118">
@@ -15546,7 +15546,7 @@
         <v/>
       </c>
       <c r="AP118" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="119">
@@ -15674,7 +15674,7 @@
         <v/>
       </c>
       <c r="AP119" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="120">
@@ -15802,7 +15802,7 @@
         <v/>
       </c>
       <c r="AP120" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="121">
@@ -15930,7 +15930,7 @@
         <v/>
       </c>
       <c r="AP121" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="122">
@@ -16058,7 +16058,7 @@
         <v/>
       </c>
       <c r="AP122" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="123">
@@ -16186,7 +16186,7 @@
         <v/>
       </c>
       <c r="AP123" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="124">
@@ -16314,7 +16314,7 @@
         <v/>
       </c>
       <c r="AP124" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="125">
@@ -16442,7 +16442,7 @@
         <v/>
       </c>
       <c r="AP125" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="126">
@@ -16570,7 +16570,7 @@
         <v/>
       </c>
       <c r="AP126" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="127">
@@ -16698,7 +16698,7 @@
         <v/>
       </c>
       <c r="AP127" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="128">
@@ -16826,7 +16826,7 @@
         <v/>
       </c>
       <c r="AP128" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="129">
@@ -16954,7 +16954,7 @@
         <v/>
       </c>
       <c r="AP129" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="130">
@@ -17082,7 +17082,7 @@
         <v/>
       </c>
       <c r="AP130" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="131">
@@ -17210,7 +17210,7 @@
         <v/>
       </c>
       <c r="AP131" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="132">
@@ -17338,7 +17338,7 @@
         <v/>
       </c>
       <c r="AP132" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="133">
@@ -17466,7 +17466,7 @@
         <v/>
       </c>
       <c r="AP133" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="134">
@@ -17594,7 +17594,7 @@
         <v/>
       </c>
       <c r="AP134" t="str">
-        <v>claude</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="135">
@@ -17722,7 +17722,7 @@
         <v/>
       </c>
       <c r="AP135" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="136">
@@ -17850,7 +17850,7 @@
         <v/>
       </c>
       <c r="AP136" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="137">
@@ -17978,7 +17978,7 @@
         <v/>
       </c>
       <c r="AP137" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="138">
@@ -18106,7 +18106,7 @@
         <v/>
       </c>
       <c r="AP138" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="139">
@@ -18234,7 +18234,7 @@
         <v/>
       </c>
       <c r="AP139" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="140">
@@ -18362,7 +18362,7 @@
         <v/>
       </c>
       <c r="AP140" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="141">
@@ -18490,7 +18490,7 @@
         <v/>
       </c>
       <c r="AP141" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="142">
@@ -18618,7 +18618,7 @@
         <v/>
       </c>
       <c r="AP142" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="143">
@@ -18746,7 +18746,7 @@
         <v/>
       </c>
       <c r="AP143" t="str">
-        <v>gemini</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="144">
@@ -18874,7 +18874,7 @@
         <v/>
       </c>
       <c r="AP144" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="145">
@@ -19002,7 +19002,7 @@
         <v/>
       </c>
       <c r="AP145" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="146">
@@ -19130,7 +19130,7 @@
         <v/>
       </c>
       <c r="AP146" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="147">
@@ -19258,7 +19258,7 @@
         <v/>
       </c>
       <c r="AP147" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="148">
@@ -19386,7 +19386,7 @@
         <v/>
       </c>
       <c r="AP148" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="149">
@@ -19514,7 +19514,7 @@
         <v/>
       </c>
       <c r="AP149" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="150">
@@ -19642,7 +19642,7 @@
         <v/>
       </c>
       <c r="AP150" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="151">
@@ -19770,7 +19770,7 @@
         <v/>
       </c>
       <c r="AP151" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="152">
@@ -19898,7 +19898,7 @@
         <v/>
       </c>
       <c r="AP152" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="153">
@@ -20026,7 +20026,7 @@
         <v/>
       </c>
       <c r="AP153" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="154">
@@ -20154,7 +20154,7 @@
         <v/>
       </c>
       <c r="AP154" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="155">
@@ -20282,7 +20282,7 @@
         <v/>
       </c>
       <c r="AP155" t="str">
-        <v>gemini</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="156">
@@ -20410,7 +20410,7 @@
         <v/>
       </c>
       <c r="AP156" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="157">
@@ -20538,7 +20538,7 @@
         <v/>
       </c>
       <c r="AP157" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="158">
@@ -20666,7 +20666,7 @@
         <v/>
       </c>
       <c r="AP158" t="str">
-        <v>claude</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="159">
@@ -20794,7 +20794,7 @@
         <v/>
       </c>
       <c r="AP159" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="160">
@@ -20922,7 +20922,7 @@
         <v/>
       </c>
       <c r="AP160" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="161">
@@ -21050,7 +21050,7 @@
         <v/>
       </c>
       <c r="AP161" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="162">
@@ -21178,7 +21178,7 @@
         <v/>
       </c>
       <c r="AP162" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="163">
@@ -21306,7 +21306,7 @@
         <v/>
       </c>
       <c r="AP163" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="164">
@@ -21434,7 +21434,7 @@
         <v/>
       </c>
       <c r="AP164" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="165">
@@ -21562,7 +21562,7 @@
         <v/>
       </c>
       <c r="AP165" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="166">
@@ -21690,7 +21690,7 @@
         <v/>
       </c>
       <c r="AP166" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="167">
@@ -21818,7 +21818,7 @@
         <v/>
       </c>
       <c r="AP167" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="168">
@@ -21946,7 +21946,7 @@
         <v/>
       </c>
       <c r="AP168" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="169">
@@ -22074,7 +22074,7 @@
         <v/>
       </c>
       <c r="AP169" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="170">
@@ -22202,7 +22202,7 @@
         <v/>
       </c>
       <c r="AP170" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="171">
@@ -22330,7 +22330,7 @@
         <v/>
       </c>
       <c r="AP171" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="172">
@@ -22458,7 +22458,7 @@
         <v/>
       </c>
       <c r="AP172" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="173">
@@ -22586,7 +22586,7 @@
         <v/>
       </c>
       <c r="AP173" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="174">
@@ -22714,7 +22714,7 @@
         <v/>
       </c>
       <c r="AP174" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="175">
@@ -22842,7 +22842,7 @@
         <v/>
       </c>
       <c r="AP175" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="176">
@@ -22970,7 +22970,7 @@
         <v/>
       </c>
       <c r="AP176" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="177">
@@ -23098,7 +23098,7 @@
         <v/>
       </c>
       <c r="AP177" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="178">
@@ -23226,7 +23226,7 @@
         <v/>
       </c>
       <c r="AP178" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="179">
@@ -23354,7 +23354,7 @@
         <v/>
       </c>
       <c r="AP179" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="180">
@@ -23482,7 +23482,7 @@
         <v/>
       </c>
       <c r="AP180" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="181">
@@ -23610,7 +23610,7 @@
         <v/>
       </c>
       <c r="AP181" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="182">
@@ -23738,7 +23738,7 @@
         <v/>
       </c>
       <c r="AP182" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="183">
@@ -23866,7 +23866,7 @@
         <v/>
       </c>
       <c r="AP183" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="184">
@@ -23994,7 +23994,7 @@
         <v/>
       </c>
       <c r="AP184" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="185">
@@ -24122,7 +24122,7 @@
         <v/>
       </c>
       <c r="AP185" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="186">
@@ -24250,7 +24250,7 @@
         <v/>
       </c>
       <c r="AP186" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="187">
@@ -24378,7 +24378,7 @@
         <v/>
       </c>
       <c r="AP187" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="188">
@@ -24506,7 +24506,7 @@
         <v/>
       </c>
       <c r="AP188" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
     <row r="189">
@@ -24634,7 +24634,7 @@
         <v/>
       </c>
       <c r="AP189" t="str">
-        <v>gpt</v>
+        <v>ai</v>
       </c>
     </row>
   </sheetData>
@@ -24646,12 +24646,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D45"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
     <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="110.83203125" customWidth="1"/>
+    <col min="4" max="4" width="112.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25127,7 +25127,7 @@
         <v>critical</v>
       </c>
       <c r="D34" t="str">
-        <v>62 rows today. NO WRITTEN DEFINITION EXISTS anywhere in the docs — see Notes.</v>
+        <v>THE BUSINESS STOPS. Licence revoked, plant shut, operations halted. 62 rows carry this today, which is a third of the library and far too many — re-rate as you go.</v>
       </c>
     </row>
     <row r="35">
@@ -25141,7 +25141,7 @@
         <v>high</v>
       </c>
       <c r="D35" t="str">
-        <v>96 rows today. No written definition — see Notes.</v>
+        <v>A fine, an enforcement action, or a finding at inspection. 96 rows today.</v>
       </c>
     </row>
     <row r="36">
@@ -25155,7 +25155,7 @@
         <v>standard</v>
       </c>
       <c r="D36" t="str">
-        <v>30 rows today. No written definition — see Notes.</v>
+        <v>A real obligation whose lapse is procedural. 30 rows today.</v>
       </c>
     </row>
     <row r="37">
@@ -25242,20 +25242,62 @@
         <v>No jurisdiction at all. Valid ONLY where source_type = contractual. A registrar contract is not territorial, and calling it federal would assert that US law requires ISO 9001.</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>generated_by</v>
+      </c>
+      <c r="B43" t="str">
+        <v>(not an enum yet)</v>
+      </c>
+      <c r="C43" t="str">
+        <v>ai</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Produced by a model. All 188 rows. Says nothing about trust — that is verification_status, which is independent of origin.</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>generated_by</v>
+      </c>
+      <c r="B44" t="str">
+        <v>(not an enum yet)</v>
+      </c>
+      <c r="C44" t="str">
+        <v>manual</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Written by a person. No row yet. A manual row is NOT automatically trustworthy — it still needs verification_status = verified.</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>cadence_type</v>
+      </c>
+      <c r="B45" t="str">
+        <v>(free text on purpose)</v>
+      </c>
+      <c r="C45" t="str">
+        <v>(anything)</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Deliberately unconstrained during this pass. Write what reads naturally; the values you actually reach for become the enum afterwards. See Notes.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D45"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C113"/>
+  <dimension ref="A1:C163"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="108.83203125" customWidth="1"/>
+    <col min="3" max="3" width="110.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25337,7 +25379,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v/>
+        <v>The second job is RE-RATING `priority` — see below, it is currently carrying no information.</v>
       </c>
       <c r="B8" t="str">
         <v/>
@@ -25348,7 +25390,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>THE SPLITTING RULE</v>
+        <v/>
       </c>
       <c r="B9" t="str">
         <v/>
@@ -25359,7 +25401,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v/>
+        <v>THE SPLITTING RULE</v>
       </c>
       <c r="B10" t="str">
         <v/>
@@ -25370,7 +25412,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Split a row when its parts have a different cadence, different evidence, or a different way of failing.</v>
+        <v/>
       </c>
       <c r="B11" t="str">
         <v/>
@@ -25381,7 +25423,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Any one of the three is enough. All three together means it is certainly more than one requirement.</v>
+        <v>Split a row when its parts have a different cadence, different evidence, or a different way of failing.</v>
       </c>
       <c r="B12" t="str">
         <v/>
@@ -25392,7 +25434,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v/>
+        <v>Any one of the three is enough. All three together means it is certainly more than one requirement.</v>
       </c>
       <c r="B13" t="str">
         <v/>
@@ -25403,7 +25445,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>The worked example: the silica standard is training AND monitoring AND written_program AND recordkeeping.</v>
+        <v/>
       </c>
       <c r="B14" t="str">
         <v/>
@@ -25414,7 +25456,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Four cadences, four kinds of evidence, four ways to fail — and one status column that can only hold one</v>
+        <v>The worked example: the silica standard is training AND monitoring AND written_program AND recordkeeping.</v>
       </c>
       <c r="B15" t="str">
         <v/>
@@ -25425,7 +25467,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>answer. A company that trained everyone but never sampled the air is compliant on one half and exposed on</v>
+        <v>Four cadences, four kinds of evidence, four ways to fail — and one status column that can only hold one</v>
       </c>
       <c r="B16" t="str">
         <v/>
@@ -25436,7 +25478,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>the other, and a single row cannot say so.</v>
+        <v>answer. A company that trained everyone but never sampled the air is compliant on one half and exposed on</v>
       </c>
       <c r="B17" t="str">
         <v/>
@@ -25447,7 +25489,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
+        <v>the other, and a single row cannot say so.</v>
       </c>
       <c r="B18" t="str">
         <v/>
@@ -25458,7 +25500,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>THE TEST: if you cannot fill in one `category` value without losing something, that is the split telling you.</v>
+        <v/>
       </c>
       <c r="B19" t="str">
         <v/>
@@ -25469,7 +25511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v/>
+        <v>THE TEST: if you cannot fill in one `category` value without losing something, that is the split telling you.</v>
       </c>
       <c r="B20" t="str">
         <v/>
@@ -25480,7 +25522,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Splitting often lets each piece name its ACTUAL enforcing agency, which the parts do not always share —</v>
+        <v/>
       </c>
       <c r="B21" t="str">
         <v/>
@@ -25491,7 +25533,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>the training half and the air-sampling half can answer to different regulators. That is a second reason to</v>
+        <v>Splitting often lets each piece name its ACTUAL enforcing agency, which the parts do not always share —</v>
       </c>
       <c r="B22" t="str">
         <v/>
@@ -25502,7 +25544,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>split, and it is invisible until you try.</v>
+        <v>the training half and the air-sampling half can answer to different regulators. That is a second reason to</v>
       </c>
       <c r="B23" t="str">
         <v/>
@@ -25513,7 +25555,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v/>
+        <v>split, and it is invisible until you try.</v>
       </c>
       <c r="B24" t="str">
         <v/>
@@ -25524,7 +25566,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>TO SPLIT A ROW:</v>
+        <v/>
       </c>
       <c r="B25" t="str">
         <v/>
@@ -25535,7 +25577,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve">  1. Keep the original row and narrow it — edit its name, cadence, evidence and fails_if down to one duty.</v>
+        <v>TO SPLIT A ROW:</v>
       </c>
       <c r="B26" t="str">
         <v/>
@@ -25546,7 +25588,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">  2. Add a new row underneath for each other duty.</v>
+        <v xml:space="preserve">  1. Keep the original row and narrow it — edit its name, cadence, evidence and fails_if down to one duty.</v>
       </c>
       <c r="B27" t="str">
         <v/>
@@ -25557,7 +25599,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v xml:space="preserve">  3. On each new row leave `id` BLANK and put the original's requirement_name in `split_from`.</v>
+        <v xml:space="preserve">  2. Add a new row underneath for each other duty.</v>
       </c>
       <c r="B28" t="str">
         <v/>
@@ -25568,7 +25610,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v xml:space="preserve">  4. requirement_name must stay unique across the whole sheet — it is the key the loader matches on.</v>
+        <v xml:space="preserve">  3. On each new row leave `id` BLANK and put the original's requirement_name in `split_from`.</v>
       </c>
       <c r="B29" t="str">
         <v/>
@@ -25579,7 +25621,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v/>
+        <v xml:space="preserve">  4. requirement_name must stay unique across the whole sheet — it is the key the loader matches on.</v>
       </c>
       <c r="B30" t="str">
         <v/>
@@ -25590,7 +25632,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>WHAT IS ALREADY PRE-FILLED, AND WHY</v>
+        <v/>
       </c>
       <c r="B31" t="str">
         <v/>
@@ -25601,7 +25643,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v/>
+        <v>WHAT `priority` MEANS — decided 10 Sep, DECISIONS.md §22.1</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -25612,7 +25654,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>3 fire-code rows carry jurisdiction_layer = local. They said `county` while naming no county. `local` means</v>
+        <v/>
       </c>
       <c r="B33" t="str">
         <v/>
@@ -25623,7 +25665,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>the authority having jurisdiction, resolved per site. Not `city`: a rural fire protection district is not a city.</v>
+        <v>THE TEST: what happens if this is missing when an inspector arrives?</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -25634,7 +25676,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>These are the first rows in the library that cannot be resolved at company level at all.</v>
+        <v/>
       </c>
       <c r="B35" t="str">
         <v/>
@@ -25645,40 +25687,40 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v/>
+        <v xml:space="preserve">  critical</v>
       </c>
       <c r="B36" t="str">
-        <v/>
+        <v>The business stops.</v>
       </c>
       <c r="C36" t="str">
-        <v/>
+        <v>Licence revoked, plant shut, operations halted.</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>3 contractual rows carry source_type = contractual and jurisdiction_layer BLANK. ISO 9001, ISO 14001 and NACD</v>
+        <v xml:space="preserve">  high</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>A fine or a finding.</v>
       </c>
       <c r="C37" t="str">
-        <v/>
+        <v>An enforcement action, or a finding at inspection.</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>are imposed by a registrar, not a government. Defaulting them to federal would assert that US federal law</v>
+        <v xml:space="preserve">  standard</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>Procedural.</v>
       </c>
       <c r="C38" t="str">
-        <v/>
+        <v>A real obligation whose lapse is procedural.</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>requires ISO 9001, which is false.</v>
+        <v/>
       </c>
       <c r="B39" t="str">
         <v/>
@@ -25689,7 +25731,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v/>
+        <v>The test is about CONSEQUENCE, not about how serious the rule sounds. A regulation can be important,</v>
       </c>
       <c r="B40" t="str">
         <v/>
@@ -25700,7 +25742,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>The other 182 rows carry source_type = statutory and their existing federal/state layer, unchanged.</v>
+        <v>well known and heavily written about, and still not stop the business if it lapses.</v>
       </c>
       <c r="B41" t="str">
         <v/>
@@ -25722,7 +25764,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>OPEN QUESTIONS EMBEDDED IN THE DATA — worth deciding during this pass</v>
+        <v>*** 62 of 188 rows are critical today — a third of everything. IF A THIRD IS CRITICAL, NOTHING IS. ***</v>
       </c>
       <c r="B43" t="str">
         <v/>
@@ -25733,7 +25775,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v/>
+        <v>A ranking that flags a third of the list as maximum severity carries no information and trains the reader</v>
       </c>
       <c r="B44" t="str">
         <v/>
@@ -25744,7 +25786,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>1. `priority` has three values and NO WRITTEN DEFINITION anywhere in the documents. 62 rows are critical,</v>
+        <v>to ignore it. Re-rate against the test above, not against the impression each rule makes.</v>
       </c>
       <c r="B45" t="str">
         <v/>
@@ -25755,7 +25797,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v xml:space="preserve">   96 high, 30 standard, and nothing records what distinguishes them. Whatever it means, it is currently</v>
+        <v/>
       </c>
       <c r="B46" t="str">
         <v/>
@@ -25766,7 +25808,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v xml:space="preserve">   the FIRST sort key on the requirements screen, so it decides what a customer sees at the top.</v>
+        <v>This matters more than it looks: `priority` is the FIRST sort key on the requirements screen, so it</v>
       </c>
       <c r="B47" t="str">
         <v/>
@@ -25777,7 +25819,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v/>
+        <v>decides what a customer sees at the top of their list. It has never had a written definition until now.</v>
       </c>
       <c r="B48" t="str">
         <v/>
@@ -25788,7 +25830,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2. `produces_switch` versus `is_determination`. is_determination is a boolean, TRUE on 9 rows.</v>
+        <v/>
       </c>
       <c r="B49" t="str">
         <v/>
@@ -25799,7 +25841,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v xml:space="preserve">   produces_switch may be the same flag renamed, or may be the NAME of the switch a row determines.</v>
+        <v>WHAT IS ALREADY PRE-FILLED, AND WHY</v>
       </c>
       <c r="B50" t="str">
         <v/>
@@ -25810,7 +25852,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v xml:space="preserve">   The design document does not say. Filter is_determination = TRUE to find the 9 rows in question.</v>
+        <v/>
       </c>
       <c r="B51" t="str">
         <v/>
@@ -25821,7 +25863,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v/>
+        <v>3 fire-code rows carry jurisdiction_layer = local. They said `county` while naming no county. `local` means</v>
       </c>
       <c r="B52" t="str">
         <v/>
@@ -25832,7 +25874,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>3. `source` versus `source_type` — two columns, unrelated meanings, confusable names. `source` is which</v>
+        <v>the authority having jurisdiction, resolved per site. Not `city`: a rural fire protection district is not a city.</v>
       </c>
       <c r="B53" t="str">
         <v/>
@@ -25843,7 +25885,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v xml:space="preserve">   MODEL wrote the row (gpt, claude, gemini). `source_type` is who IMPOSES the duty. Renaming `source` to</v>
+        <v>These are the first rows in the library that cannot be resolved at company level at all.</v>
       </c>
       <c r="B54" t="str">
         <v/>
@@ -25854,7 +25896,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v xml:space="preserve">   `generated_by` before the rebuild would cost nothing now and remove the trap permanently.</v>
+        <v/>
       </c>
       <c r="B55" t="str">
         <v/>
@@ -25865,7 +25907,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v/>
+        <v>3 contractual rows carry source_type = contractual and jurisdiction_layer BLANK. ISO 9001, ISO 14001 and NACD</v>
       </c>
       <c r="B56" t="str">
         <v/>
@@ -25876,7 +25918,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>4. `cadence_type` is left as free text here because its vocabulary is not settled. Fill it in however reads</v>
+        <v>are imposed by a registrar, not a government. Defaulting them to federal would assert that US federal law</v>
       </c>
       <c r="B57" t="str">
         <v/>
@@ -25887,7 +25929,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v xml:space="preserve">   naturally; the values you actually use are better evidence for the enum than a list guessed in advance.</v>
+        <v>requires ISO 9001, which is false.</v>
       </c>
       <c r="B58" t="str">
         <v/>
@@ -25909,7 +25951,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>COLUMN REFERENCE</v>
+        <v>The other 182 rows carry source_type = statutory and their existing federal/state layer, unchanged.</v>
       </c>
       <c r="B60" t="str">
         <v/>
@@ -25931,480 +25973,480 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Column</v>
+        <v>generated_by = ai on all 188. This replaces the old `source` column (gpt/claude/gemini) — see below.</v>
       </c>
       <c r="B62" t="str">
-        <v>Status</v>
+        <v/>
       </c>
       <c r="C62" t="str">
-        <v>What it is</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>id</v>
+        <v/>
       </c>
       <c r="B63" t="str">
-        <v>spreadsheet only</v>
+        <v/>
       </c>
       <c r="C63" t="str">
-        <v>The current row's database id. Do not edit. LEAVE BLANK on any new row you create by splitting.</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>split_from</v>
+        <v>COLUMNS THAT STAY EMPTY, AND WHY</v>
       </c>
       <c r="B64" t="str">
-        <v>spreadsheet only</v>
+        <v/>
       </c>
       <c r="C64" t="str">
-        <v>On a new row created by a split, the requirement_name of the row it came from. Blank on every original row.</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>version</v>
+        <v/>
       </c>
       <c r="B65" t="str">
-        <v>carried over</v>
+        <v/>
       </c>
       <c r="C65" t="str">
-        <v>Library version. 1 for every row here. A later change creates version 2, it never edits this row.</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>supersedes_id</v>
+        <v>produces_switch — it holds the NAME of the switch a row determines, not a renamed is_determination.</v>
       </c>
       <c r="B66" t="str">
-        <v>stays empty for now</v>
+        <v/>
       </c>
       <c r="C66" t="str">
-        <v>The id of the version this row replaces. Blank at version 1.</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>effective_from</v>
+        <v xml:space="preserve">  The two coexist and both are needed: the boolean says a row determines something, the name says WHAT,</v>
       </c>
       <c r="B67" t="str">
-        <v>YOURS TO FILL</v>
+        <v/>
       </c>
       <c r="C67" t="str">
-        <v>Date this version became the active one (YYYY-MM-DD). Blank is acceptable for now.</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>effective_to</v>
+        <v xml:space="preserve">  and the resolution engine needs the second to write the value back. It stays blank through this pass</v>
       </c>
       <c r="B68" t="str">
-        <v>stays empty for now</v>
+        <v/>
       </c>
       <c r="C68" t="str">
-        <v>Set only when a later version supersedes this row. Always blank here.</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>requirement_name</v>
+        <v xml:space="preserve">  because THE SWITCH LIBRARY DOES NOT EXIST UNTIL 6.2 — there are no names to reference yet, and inventing</v>
       </c>
       <c r="B69" t="str">
-        <v>carried over</v>
+        <v/>
       </c>
       <c r="C69" t="str">
-        <v>What the requirement is. Unique across the table — it is the key the loader matches on.</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>category</v>
+        <v xml:space="preserve">  identifiers now means the switch library has to match them later. is_determination is carried across so</v>
       </c>
       <c r="B70" t="str">
-        <v>YOURS TO FILL</v>
+        <v/>
       </c>
       <c r="C70" t="str">
-        <v>*** THE MAIN COLUMN OF THIS PASS. *** The new obligation type. One of ten values — see Reference. EMPTY ON EVERY ROW BY DESIGN.</v>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>category_current</v>
+        <v xml:space="preserve">  the 9 rows stay findable: filter is_determination = TRUE when there is something to point them at.</v>
       </c>
       <c r="B71" t="str">
-        <v>spreadsheet only</v>
+        <v/>
       </c>
       <c r="C71" t="str">
-        <v>The old 26-value category, for reference while you map. Not loaded. Never edit this.</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>entity_type</v>
+        <v/>
       </c>
       <c r="B72" t="str">
-        <v>carried over</v>
+        <v/>
       </c>
       <c r="C72" t="str">
-        <v>What the requirement attaches to: organization, site, chemical, equipment, person, product.</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>source_type</v>
+        <v>cadence_type — FREE TEXT ON PURPOSE. Write whatever reads naturally. The vocabulary is not settled, and</v>
       </c>
       <c r="B73" t="str">
-        <v>PRE-FILLED from a decision</v>
+        <v/>
       </c>
       <c r="C73" t="str">
-        <v>Who imposes it: statutory or contractual. Pre-filled — three rows are contractual, the other 185 statutory.</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>jurisdiction_layer</v>
+        <v xml:space="preserve">  the values you reach for while categorising 188 real requirements are better evidence for the enum than</v>
       </c>
       <c r="B74" t="str">
-        <v>PRE-FILLED from a decision</v>
+        <v/>
       </c>
       <c r="C74" t="str">
-        <v>Which government's law reaches here. Pre-filled from the old `layer`, with the six flagged rows already corrected.</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>jurisdiction_state</v>
+        <v xml:space="preserve">  a list guessed in advance. IT BECOMES AN ENUM AFTER THIS PASS, built from what you actually used. The</v>
       </c>
       <c r="B75" t="str">
-        <v>carried over</v>
+        <v/>
       </c>
       <c r="C75" t="str">
-        <v>State name, e.g. Oregon. Blank on federal rows.</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>jurisdiction_county</v>
+        <v xml:space="preserve">  cost of waiting is one migration; the cost of guessing wrong is a vocabulary the data cannot be</v>
       </c>
       <c r="B76" t="str">
-        <v>YOURS TO FILL</v>
+        <v/>
       </c>
       <c r="C76" t="str">
-        <v>Required when jurisdiction_layer = county. Empty in all 188 rows today.</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>jurisdiction_city</v>
+        <v xml:space="preserve">  expressed in, or an `other` value that swallows every hard case. Note that `cadence` — the prose — is</v>
       </c>
       <c r="B77" t="str">
-        <v>YOURS TO FILL</v>
+        <v/>
       </c>
       <c r="C77" t="str">
-        <v>Required when jurisdiction_layer = city.</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>industries</v>
+        <v xml:space="preserve">  kept regardless and is never replaced by cadence_type.</v>
       </c>
       <c r="B78" t="str">
-        <v>carried over</v>
+        <v/>
       </c>
       <c r="C78" t="str">
-        <v>Semicolon-separated list. Pre-filled from the single `industry` value. One row can serve several verticals.</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>agency_id</v>
+        <v/>
       </c>
       <c r="B79" t="str">
-        <v>stays empty for now</v>
+        <v/>
       </c>
       <c r="C79" t="str">
-        <v>The enforcing agency. Blank everywhere — the agencies table holds zero rows. Phase 2.1.</v>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>secondary_agency_ids</v>
+        <v>agency_id, citation_url, citation_quote, source_checked_at, verified_by, verified_at, applies_expression —</v>
       </c>
       <c r="B80" t="str">
-        <v>stays empty for now</v>
+        <v/>
       </c>
       <c r="C80" t="str">
-        <v>Semicolon-separated. Other agencies with an interest. Phase 2.1.</v>
+        <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>citation</v>
+        <v xml:space="preserve">  these are Phase 6 and 7 work. agency_id in particular cannot be filled: the agencies table holds 0 rows.</v>
       </c>
       <c r="B81" t="str">
-        <v>carried over</v>
+        <v/>
       </c>
       <c r="C81" t="str">
-        <v>The enforcing citation. Oregon is a State Plan state — cite OAR 437, not 29 CFR.</v>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>citation_url</v>
+        <v/>
       </c>
       <c r="B82" t="str">
-        <v>stays empty for now</v>
+        <v/>
       </c>
       <c r="C82" t="str">
-        <v>Primary source link. Phase 6.6, by retrieval — never from memory.</v>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>citation_quote</v>
+        <v>`source` BECAME `generated_by` — DECISIONS.md §22.3</v>
       </c>
       <c r="B83" t="str">
-        <v>stays empty for now</v>
+        <v/>
       </c>
       <c r="C83" t="str">
-        <v>The operative sentence, retrieved verbatim. Phase 6.6.</v>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>citation_federal_analogue</v>
+        <v/>
       </c>
       <c r="B84" t="str">
-        <v>YOURS TO FILL</v>
+        <v/>
       </c>
       <c r="C84" t="str">
-        <v>The federal reference a state rule mirrors, for context only. Optional.</v>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>source_checked_at</v>
+        <v>Two values now: ai | manual. claude, gpt and gemini all map to ai.</v>
       </c>
       <c r="B85" t="str">
-        <v>stays empty for now</v>
+        <v/>
       </c>
       <c r="C85" t="str">
-        <v>When the citation was last checked against the primary source. Phase 6.6.</v>
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>applies</v>
+        <v/>
       </c>
       <c r="B86" t="str">
-        <v>carried over</v>
+        <v/>
       </c>
       <c r="C86" t="str">
-        <v>conditional or universal. 182 of 188 are conditional — determination is the product.</v>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>applies_expression</v>
+        <v>The model name drove no decision — nothing in the product treats a GPT row differently from a Claude row.</v>
       </c>
       <c r="B87" t="str">
-        <v>stays empty for now</v>
+        <v/>
       </c>
       <c r="C87" t="str">
-        <v>Machine-evaluable form of the trigger. Phase 6.3, five days of work. Blank here.</v>
+        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>trigger_condition</v>
+        <v>TRUST IS A SEPARATE AXIS, carried by verification_status (generated | disputed | verified) and independent</v>
       </c>
       <c r="B88" t="str">
-        <v>carried over</v>
+        <v/>
       </c>
       <c r="C88" t="str">
-        <v>The condition in prose. Blank on the 6 universal rows.</v>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>trigger_plain</v>
+        <v>of origin: a manual row can be unverified, an AI row can be primary-source verified.</v>
       </c>
       <c r="B89" t="str">
-        <v>carried over</v>
+        <v/>
       </c>
       <c r="C89" t="str">
-        <v>The same condition in plain language for the user.</v>
+        <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>scope_rules</v>
+        <v/>
       </c>
       <c r="B90" t="str">
-        <v>YOURS TO FILL</v>
+        <v/>
       </c>
       <c r="C90" t="str">
-        <v>What this requirement does NOT cover, and its common misreading. New — see Notes.</v>
+        <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>produces_switch</v>
+        <v>The rename also removes a trap — `source` and `source_type` sat adjacent with unrelated meanings.</v>
       </c>
       <c r="B91" t="str">
-        <v>YOURS TO FILL</v>
+        <v/>
       </c>
       <c r="C91" t="str">
-        <v>The switch this row determines, if any. See the open question in Notes.</v>
+        <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>is_determination</v>
+        <v/>
       </c>
       <c r="B92" t="str">
-        <v>carried over</v>
+        <v/>
       </c>
       <c r="C92" t="str">
-        <v>Current boolean flag. TRUE on 9 rows. Its relationship to produces_switch is undecided.</v>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>cadence_type</v>
+        <v>WHAT THE OLD 174 / 11 / 3 SPLIT ACTUALLY MEANT, since it is easy to misread:</v>
       </c>
       <c r="B93" t="str">
-        <v>YOURS TO FILL</v>
+        <v/>
       </c>
       <c r="C93" t="str">
-        <v>The shape of the timing, as one value. Free text for now — the vocabulary is not settled.</v>
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>cadence_anchor</v>
+        <v>The merge was SEQUENTIAL, not competitive. GPT generated first (174 rows). Claude ran next and added 11</v>
       </c>
       <c r="B94" t="str">
-        <v>YOURS TO FILL</v>
+        <v/>
       </c>
       <c r="C94" t="str">
-        <v>The fixed point, e.g. "March 1" or "anniversary of issue".</v>
+        <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>cadence</v>
+        <v>GPT had missed. Gemini ran last and added 3 the other two had missed. All three lists were merged; nothing</v>
       </c>
       <c r="B95" t="str">
-        <v>carried over</v>
+        <v/>
       </c>
       <c r="C95" t="str">
-        <v>The full timing in prose. KEEP IT — it is irreducible and 100% populated. cadence_type never replaces it.</v>
+        <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>evidence_description</v>
+        <v>was chosen between and no row was discarded. So the column was a BUILD LOG — which model first contributed</v>
       </c>
       <c r="B96" t="str">
-        <v>carried over</v>
+        <v/>
       </c>
       <c r="C96" t="str">
-        <v>What proves this requirement is met.</v>
+        <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>evidence_types</v>
+        <v>a row the others lacked — not authorship, not a quality ranking, and not a tie-break.</v>
       </c>
       <c r="B97" t="str">
-        <v>YOURS TO FILL</v>
+        <v/>
       </c>
       <c r="C97" t="str">
-        <v>Semicolon-separated shorthand for the kinds of document that satisfy it.</v>
+        <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>fails_if</v>
+        <v/>
       </c>
       <c r="B98" t="str">
-        <v>carried over</v>
+        <v/>
       </c>
       <c r="C98" t="str">
-        <v>What a failure looks like. This is what makes a split visible — see Notes.</v>
+        <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>priority</v>
+        <v>What that split IS worth keeping is a CONVERGENCE SIGNAL: 174, then +11, then +3. Each model found</v>
       </c>
       <c r="B99" t="str">
-        <v>carried over</v>
+        <v/>
       </c>
       <c r="C99" t="str">
-        <v>critical, high or standard. No written definition exists — see Notes.</v>
+        <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>status</v>
+        <v>dramatically less than the one before. Weak evidence, because three models on overlapping corpora can</v>
       </c>
       <c r="B100" t="str">
-        <v>carried over</v>
+        <v/>
       </c>
       <c r="C100" t="str">
-        <v>Verification status. Every row is `generated`. Only a person may set `verified`.</v>
+        <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>verification_note</v>
+        <v>share a blind spot — a requirement none of them knows about produces this same curve. But real evidence,</v>
       </c>
       <c r="B101" t="str">
-        <v>stays empty for now</v>
+        <v/>
       </c>
       <c r="C101" t="str">
-        <v>Why a row is disputed, or what was checked to verify it. Phase 6.7.</v>
+        <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>verified_by</v>
+        <v>because the drop is that steep: if substantial territory were missing, the third model would not have</v>
       </c>
       <c r="B102" t="str">
-        <v>stays empty for now</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>Who verified it. Phase 6.7. A person, never the worker.</v>
+        <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>verified_at</v>
+        <v>found only three rows. That curve is why a FOURTH model was not run — expected yield about one row. The</v>
       </c>
       <c r="B103" t="str">
-        <v>stays empty for now</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>When. Phase 6.7.</v>
+        <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>source</v>
+        <v>shared blind spot is closed by primary-source retrieval against each agency's published scope, not by</v>
       </c>
       <c r="B104" t="str">
-        <v>carried over</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>Which model produced the row: gpt, claude, gemini. NOT the same as source_type.</v>
+        <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v/>
+        <v>another opinion of the same kind.</v>
       </c>
       <c r="B105" t="str">
         <v/>
@@ -26415,7 +26457,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>LOADING IT BACK</v>
+        <v/>
       </c>
       <c r="B106" t="str">
         <v/>
@@ -26426,7 +26468,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v/>
+        <v>COLUMN REFERENCE</v>
       </c>
       <c r="B107" t="str">
         <v/>
@@ -26437,7 +26479,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Do not paste into the database. The loader validates first and refuses the whole file on any error,</v>
+        <v/>
       </c>
       <c r="B108" t="str">
         <v/>
@@ -26448,62 +26490,612 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>so a bad value can never land as a half-applied change. See the reply that came with this file.</v>
+        <v>Column</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>Status</v>
       </c>
       <c r="C109" t="str">
-        <v/>
+        <v>What it is</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v/>
+        <v>id</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>spreadsheet only</v>
       </c>
       <c r="C110" t="str">
-        <v/>
+        <v>The current row's database id. Do not edit. LEAVE BLANK on any new row you create by splitting.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>The checks it runs: every category filled and in the ten values; requirement_name unique; every</v>
+        <v>split_from</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>spreadsheet only</v>
       </c>
       <c r="C111" t="str">
-        <v/>
+        <v>On a new row created by a split, the requirement_name of the row it came from. Blank on every original row.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>split_from naming a row that exists; jurisdiction_county filled where layer = county and city where</v>
+        <v>version</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>carried over</v>
       </c>
       <c r="C112" t="str">
-        <v/>
+        <v>Library version. 1 for every row here. A later change creates version 2, it never edits this row.</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>layer = city; jurisdiction_layer blank ONLY where source_type = contractual; every enum value legal.</v>
+        <v>supersedes_id</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>stays empty for now</v>
       </c>
       <c r="C113" t="str">
+        <v>The id of the version this row replaces. Blank at version 1.</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>effective_from</v>
+      </c>
+      <c r="B114" t="str">
+        <v>YOURS TO FILL</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Date this version became the active one (YYYY-MM-DD). Blank is acceptable for now.</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>effective_to</v>
+      </c>
+      <c r="B115" t="str">
+        <v>stays empty for now</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Set only when a later version supersedes this row. Always blank here.</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>requirement_name</v>
+      </c>
+      <c r="B116" t="str">
+        <v>carried over</v>
+      </c>
+      <c r="C116" t="str">
+        <v>What the requirement is. Unique across the table — it is the key the loader matches on.</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>category</v>
+      </c>
+      <c r="B117" t="str">
+        <v>YOURS TO FILL</v>
+      </c>
+      <c r="C117" t="str">
+        <v>*** THE MAIN COLUMN OF THIS PASS. *** The new obligation type. One of ten values — see Reference. EMPTY ON EVERY ROW BY DESIGN.</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>category_current</v>
+      </c>
+      <c r="B118" t="str">
+        <v>spreadsheet only</v>
+      </c>
+      <c r="C118" t="str">
+        <v>The old 26-value category, for reference while you map. Not loaded. Never edit this.</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>entity_type</v>
+      </c>
+      <c r="B119" t="str">
+        <v>carried over</v>
+      </c>
+      <c r="C119" t="str">
+        <v>What the requirement attaches to: organization, site, chemical, equipment, person, product.</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>source_type</v>
+      </c>
+      <c r="B120" t="str">
+        <v>PRE-FILLED from a decision</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Who imposes it: statutory or contractual. Pre-filled — three rows are contractual, the other 185 statutory.</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>jurisdiction_layer</v>
+      </c>
+      <c r="B121" t="str">
+        <v>PRE-FILLED from a decision</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Which government's law reaches here. Pre-filled from the old `layer`, with the six flagged rows already corrected.</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>jurisdiction_state</v>
+      </c>
+      <c r="B122" t="str">
+        <v>carried over</v>
+      </c>
+      <c r="C122" t="str">
+        <v>State name, e.g. Oregon. Blank on federal rows.</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>jurisdiction_county</v>
+      </c>
+      <c r="B123" t="str">
+        <v>YOURS TO FILL</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Required when jurisdiction_layer = county. Empty in all 188 rows today.</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>jurisdiction_city</v>
+      </c>
+      <c r="B124" t="str">
+        <v>YOURS TO FILL</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Required when jurisdiction_layer = city.</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>industries</v>
+      </c>
+      <c r="B125" t="str">
+        <v>carried over</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Semicolon-separated list. Pre-filled from the single `industry` value. One row can serve several verticals.</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>agency_id</v>
+      </c>
+      <c r="B126" t="str">
+        <v>stays empty for now</v>
+      </c>
+      <c r="C126" t="str">
+        <v>The enforcing agency. Blank everywhere — the agencies table holds zero rows. Phase 2.1.</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>secondary_agency_ids</v>
+      </c>
+      <c r="B127" t="str">
+        <v>stays empty for now</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Semicolon-separated. Other agencies with an interest. Phase 2.1.</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>citation</v>
+      </c>
+      <c r="B128" t="str">
+        <v>carried over</v>
+      </c>
+      <c r="C128" t="str">
+        <v>The enforcing citation. Oregon is a State Plan state — cite OAR 437, not 29 CFR.</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>citation_url</v>
+      </c>
+      <c r="B129" t="str">
+        <v>stays empty for now</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Primary source link. Phase 6.6, by retrieval — never from memory.</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>citation_quote</v>
+      </c>
+      <c r="B130" t="str">
+        <v>stays empty for now</v>
+      </c>
+      <c r="C130" t="str">
+        <v>The operative sentence, retrieved verbatim. Phase 6.6.</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>citation_federal_analogue</v>
+      </c>
+      <c r="B131" t="str">
+        <v>YOURS TO FILL</v>
+      </c>
+      <c r="C131" t="str">
+        <v>The federal reference a state rule mirrors, for context only. Optional.</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>source_checked_at</v>
+      </c>
+      <c r="B132" t="str">
+        <v>stays empty for now</v>
+      </c>
+      <c r="C132" t="str">
+        <v>When the citation was last checked against the primary source. Phase 6.6.</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>applies</v>
+      </c>
+      <c r="B133" t="str">
+        <v>carried over</v>
+      </c>
+      <c r="C133" t="str">
+        <v>conditional or universal. 182 of 188 are conditional — determination is the product.</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>applies_expression</v>
+      </c>
+      <c r="B134" t="str">
+        <v>stays empty for now</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Machine-evaluable form of the trigger. Phase 6.3, five days of work. Blank here.</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>trigger_condition</v>
+      </c>
+      <c r="B135" t="str">
+        <v>carried over</v>
+      </c>
+      <c r="C135" t="str">
+        <v>The condition in prose. Blank on the 6 universal rows.</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>trigger_plain</v>
+      </c>
+      <c r="B136" t="str">
+        <v>carried over</v>
+      </c>
+      <c r="C136" t="str">
+        <v>The same condition in plain language for the user.</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>scope_rules</v>
+      </c>
+      <c r="B137" t="str">
+        <v>YOURS TO FILL</v>
+      </c>
+      <c r="C137" t="str">
+        <v>What this requirement does NOT cover, and its common misreading. New — see Notes.</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>produces_switch</v>
+      </c>
+      <c r="B138" t="str">
+        <v>stays empty for now</v>
+      </c>
+      <c r="C138" t="str">
+        <v>The NAME of the switch this row determines. Stays blank — the switch library does not exist until 6.2.</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>is_determination</v>
+      </c>
+      <c r="B139" t="str">
+        <v>carried over</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Boolean: does this row determine a switch. TRUE on 9 rows. Keeps them findable until produces_switch can be filled.</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>cadence_type</v>
+      </c>
+      <c r="B140" t="str">
+        <v>YOURS TO FILL</v>
+      </c>
+      <c r="C140" t="str">
+        <v>The shape of the timing, as one value. FREE TEXT on purpose — it becomes an enum after this pass, from what you actually use.</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>cadence_anchor</v>
+      </c>
+      <c r="B141" t="str">
+        <v>YOURS TO FILL</v>
+      </c>
+      <c r="C141" t="str">
+        <v>The fixed point, e.g. "March 1" or "anniversary of issue".</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>cadence</v>
+      </c>
+      <c r="B142" t="str">
+        <v>carried over</v>
+      </c>
+      <c r="C142" t="str">
+        <v>The full timing in prose. KEEP IT — it is irreducible and 100% populated. cadence_type never replaces it.</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>evidence_description</v>
+      </c>
+      <c r="B143" t="str">
+        <v>carried over</v>
+      </c>
+      <c r="C143" t="str">
+        <v>What proves this requirement is met.</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>evidence_types</v>
+      </c>
+      <c r="B144" t="str">
+        <v>YOURS TO FILL</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Semicolon-separated shorthand for the kinds of document that satisfy it.</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>fails_if</v>
+      </c>
+      <c r="B145" t="str">
+        <v>carried over</v>
+      </c>
+      <c r="C145" t="str">
+        <v>What a failure looks like. This is what makes a split visible — see Notes.</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>priority</v>
+      </c>
+      <c r="B146" t="str">
+        <v>carried over</v>
+      </c>
+      <c r="C146" t="str">
+        <v>critical, high or standard — now defined by consequence. See Notes. 62 rows are critical today and that is too many.</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>status</v>
+      </c>
+      <c r="B147" t="str">
+        <v>carried over</v>
+      </c>
+      <c r="C147" t="str">
+        <v>Verification status. Every row is `generated`. Only a person may set `verified`. Independent of generated_by.</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>verification_note</v>
+      </c>
+      <c r="B148" t="str">
+        <v>stays empty for now</v>
+      </c>
+      <c r="C148" t="str">
+        <v>Why a row is disputed, or what was checked to verify it. Phase 6.7.</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>verified_by</v>
+      </c>
+      <c r="B149" t="str">
+        <v>stays empty for now</v>
+      </c>
+      <c r="C149" t="str">
+        <v>Who verified it. Phase 6.7. A person, never the worker.</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>verified_at</v>
+      </c>
+      <c r="B150" t="str">
+        <v>stays empty for now</v>
+      </c>
+      <c r="C150" t="str">
+        <v>When. Phase 6.7.</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>generated_by</v>
+      </c>
+      <c r="B151" t="str">
+        <v>PRE-FILLED from a decision</v>
+      </c>
+      <c r="C151" t="str">
+        <v>ai or manual. Origin only — was `source` (gpt/claude/gemini), collapsed because the model name drives no decision.</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v/>
+      </c>
+      <c r="B152" t="str">
+        <v/>
+      </c>
+      <c r="C152" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>LOADING IT BACK</v>
+      </c>
+      <c r="B153" t="str">
+        <v/>
+      </c>
+      <c r="C153" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v/>
+      </c>
+      <c r="B154" t="str">
+        <v/>
+      </c>
+      <c r="C154" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>Do not paste into the database. The loader validates the whole file first and refuses it entirely on</v>
+      </c>
+      <c r="B155" t="str">
+        <v/>
+      </c>
+      <c r="C155" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>any error, so a bad value can never land as a half-applied change. It dry-runs before it writes, and</v>
+      </c>
+      <c r="B156" t="str">
+        <v/>
+      </c>
+      <c r="C156" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>goes to staging before production.</v>
+      </c>
+      <c r="B157" t="str">
+        <v/>
+      </c>
+      <c r="C157" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v/>
+      </c>
+      <c r="B158" t="str">
+        <v/>
+      </c>
+      <c r="C158" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>The checks it runs: every category filled and one of the ten values; requirement_name unique; every</v>
+      </c>
+      <c r="B159" t="str">
+        <v/>
+      </c>
+      <c r="C159" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>split_from naming a row that exists; every blank-id row having a split_from; jurisdiction_county filled</v>
+      </c>
+      <c r="B160" t="str">
+        <v/>
+      </c>
+      <c r="C160" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>where layer = county and city where layer = city; jurisdiction_layer blank ONLY where source_type =</v>
+      </c>
+      <c r="B161" t="str">
+        <v/>
+      </c>
+      <c r="C161" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>contractual; generated_by one of ai|manual; every enum value legal against the live catalog; and every</v>
+      </c>
+      <c r="B162" t="str">
+        <v/>
+      </c>
+      <c r="C162" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>one of the 188 original ids still accounted for.</v>
+      </c>
+      <c r="B163" t="str">
+        <v/>
+      </c>
+      <c r="C163" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C113"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C163"/>
   </ignoredErrors>
 </worksheet>
 </file>